--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -1,20 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FCD56-ED9A-4709-8E48-54BDEC2B27DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="SEM-1"/>
+    <sheet name="SEM-1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="156">
   <si>
     <t>Exam_SEAT_NO</t>
   </si>
@@ -479,13 +496,15 @@
   </si>
   <si>
     <t>MOTHER_25</t>
+  </si>
+  <si>
+    <t>IMAGE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -535,71 +554,1319 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="17" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="17" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="17" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6E39CA9-6D42-83C1-A90E-DE3749E97CFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A8EB787-CE50-495D-9775-D7B5BE985218}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2390EB03-6DE7-4B65-8121-34D7B009CA47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65688A18-3F3A-4C18-8B46-2B328023C5A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{487998ED-84C8-460B-BF5D-2F093E62BD6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{888023CE-7B64-4FD8-BBDC-19C86DBDB162}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{587515D0-5833-4EF7-A175-3F0BF54CE5B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE74D4ED-D9C5-429F-BB25-79D7608A282A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BF2B5CD-4869-4077-A151-6B3C36F72AE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DD6C39-E34E-4D71-A7E1-8B5A10409168}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314E1937-38DA-4D18-8E2D-4A2775C7A3A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938CA0B9-859C-49DD-A781-E1562AC28E0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8233333-B91F-4026-B0D0-4041F4892341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECC6A20B-B9AF-4FEA-9799-E2573748A2FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F13D5AA-3662-49FB-AC37-E91CF0EC7740}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C3D1FA-A758-4B7A-B4F3-7C82DFDDFF59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD883E3E-C398-49D1-B61B-E520EEEE7B8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B2AEAE3-1786-4CE1-809B-61C8974F11CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{418110DA-172D-401E-B6CB-5FC17BF9C269}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8A74893-F1DB-4235-A0BD-1EE7EC0BAE2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9C97F30-8259-481F-90B3-26B2FEB99C5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B95D20F4-ADD5-4E5A-90B3-2541A157DB50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFBA6DA-A126-4B61-9C5E-9A1D32BFEF1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{650A8987-546F-489E-B3DA-18148FBADFFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>2552700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1716024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77E713A-CC3A-4CD3-A0C0-2B03C5DF258D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54864000" y="624840"/>
+          <a:ext cx="2377440" cy="1335024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,10 +1874,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -648,71 +1915,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -740,7 +2007,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -763,11 +2030,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -776,13 +2043,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -792,7 +2059,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -801,7 +2068,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -810,7 +2077,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -818,10 +2085,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -886,62 +2153,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AT26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AU26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="13" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="15" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="25.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="9.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="21.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="14" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="14" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="14" width="21.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="14" width="25.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="14" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="13" width="14.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="13" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="13" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="13" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="13" width="16.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="17" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="14" width="7.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="22.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="19.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,45 +2348,49 @@
       <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="AU1" s="15" t="s">
+        <v>155</v>
+      </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:47" ht="119.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>112233</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>38838</v>
       </c>
-      <c r="H2" s="9">
-        <f>"ABC-"&amp;B2</f>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="H2" t="str">
+        <f t="shared" ref="H2:H26" si="0">"ABC-"&amp;B2</f>
+        <v>ABC-112233</v>
+      </c>
+      <c r="I2" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="8">
         <v>43952</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L2" s="6">
         <v>1</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" t="s">
         <v>52</v>
       </c>
       <c r="N2" s="6">
@@ -1133,7 +2405,7 @@
       <c r="Q2" s="6">
         <v>17</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" t="s">
         <v>53</v>
       </c>
       <c r="S2" s="6">
@@ -1148,7 +2420,7 @@
       <c r="V2" s="6">
         <v>24</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" t="s">
         <v>54</v>
       </c>
       <c r="X2" s="6">
@@ -1163,7 +2435,7 @@
       <c r="AA2" s="6">
         <v>23</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AB2" t="s">
         <v>55</v>
       </c>
       <c r="AC2" s="6">
@@ -1178,7 +2450,7 @@
       <c r="AF2" s="6">
         <v>20</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AG2" t="s">
         <v>56</v>
       </c>
       <c r="AH2" s="6">
@@ -1193,7 +2465,7 @@
       <c r="AK2" s="6">
         <v>15</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AL2" t="s">
         <v>57</v>
       </c>
       <c r="AM2" s="6">
@@ -1212,53 +2484,56 @@
         <v>750</v>
       </c>
       <c r="AR2" s="6">
-        <f>SUM(N2:AP2)</f>
-      </c>
-      <c r="AS2" s="12">
-        <f>AR2/AQ2*100</f>
-      </c>
-      <c r="AT2" s="7" t="s">
+        <f t="shared" ref="AR2:AR26" si="1">SUM(N2:AP2)</f>
+        <v>618</v>
+      </c>
+      <c r="AS2" s="10">
+        <f t="shared" ref="AS2:AS26" si="2">AR2/AQ2*100</f>
+        <v>82.399999999999991</v>
+      </c>
+      <c r="AT2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:47" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="6">
         <v>112234</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>38839</v>
       </c>
-      <c r="H3" s="9">
-        <f>"ABC-"&amp;B3</f>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="H3" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112234</v>
+      </c>
+      <c r="I3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>43952</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L3" s="6">
         <v>1</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" t="s">
         <v>52</v>
       </c>
       <c r="N3" s="6">
@@ -1273,7 +2548,7 @@
       <c r="Q3" s="6">
         <v>20</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" t="s">
         <v>53</v>
       </c>
       <c r="S3" s="6">
@@ -1288,7 +2563,7 @@
       <c r="V3" s="6">
         <v>18</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" t="s">
         <v>54</v>
       </c>
       <c r="X3" s="6">
@@ -1303,7 +2578,7 @@
       <c r="AA3" s="6">
         <v>10</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AB3" t="s">
         <v>55</v>
       </c>
       <c r="AC3" s="6">
@@ -1318,7 +2593,7 @@
       <c r="AF3" s="6">
         <v>15</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AG3" t="s">
         <v>56</v>
       </c>
       <c r="AH3" s="6">
@@ -1333,7 +2608,7 @@
       <c r="AK3" s="6">
         <v>10</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AL3" t="s">
         <v>57</v>
       </c>
       <c r="AM3" s="6">
@@ -1352,53 +2627,56 @@
         <v>750</v>
       </c>
       <c r="AR3" s="6">
-        <f>SUM(N3:AP3)</f>
-      </c>
-      <c r="AS3" s="12">
-        <f>AR3/AQ3*100</f>
-      </c>
-      <c r="AT3" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>567</v>
+      </c>
+      <c r="AS3" s="10">
+        <f t="shared" si="2"/>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AT3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="6">
         <v>112235</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>38840</v>
       </c>
-      <c r="H4" s="9">
-        <f>"ABC-"&amp;B4</f>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112235</v>
+      </c>
+      <c r="I4" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="8">
         <v>43952</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L4" s="6">
         <v>1</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" t="s">
         <v>52</v>
       </c>
       <c r="N4" s="6">
@@ -1413,7 +2691,7 @@
       <c r="Q4" s="6">
         <v>23</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" t="s">
         <v>53</v>
       </c>
       <c r="S4" s="6">
@@ -1428,7 +2706,7 @@
       <c r="V4" s="6">
         <v>15</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="W4" t="s">
         <v>54</v>
       </c>
       <c r="X4" s="6">
@@ -1443,7 +2721,7 @@
       <c r="AA4" s="6">
         <v>22</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AB4" t="s">
         <v>55</v>
       </c>
       <c r="AC4" s="6">
@@ -1458,7 +2736,7 @@
       <c r="AF4" s="6">
         <v>23</v>
       </c>
-      <c r="AG4" s="7" t="s">
+      <c r="AG4" t="s">
         <v>56</v>
       </c>
       <c r="AH4" s="6">
@@ -1473,7 +2751,7 @@
       <c r="AK4" s="6">
         <v>22</v>
       </c>
-      <c r="AL4" s="7" t="s">
+      <c r="AL4" t="s">
         <v>57</v>
       </c>
       <c r="AM4" s="6">
@@ -1492,53 +2770,56 @@
         <v>750</v>
       </c>
       <c r="AR4" s="6">
-        <f>SUM(N4:AP4)</f>
-      </c>
-      <c r="AS4" s="12">
-        <f>AR4/AQ4*100</f>
-      </c>
-      <c r="AT4" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="AS4" s="10">
+        <f t="shared" si="2"/>
+        <v>85.333333333333343</v>
+      </c>
+      <c r="AT4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6">
         <v>112236</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>38841</v>
       </c>
-      <c r="H5" s="9">
-        <f>"ABC-"&amp;B5</f>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112236</v>
+      </c>
+      <c r="I5" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="8">
         <v>43952</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" t="s">
         <v>52</v>
       </c>
       <c r="N5" s="6">
@@ -1553,7 +2834,7 @@
       <c r="Q5" s="6">
         <v>22</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" t="s">
         <v>53</v>
       </c>
       <c r="S5" s="6">
@@ -1568,7 +2849,7 @@
       <c r="V5" s="6">
         <v>23</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="W5" t="s">
         <v>54</v>
       </c>
       <c r="X5" s="6">
@@ -1583,7 +2864,7 @@
       <c r="AA5" s="6">
         <v>22</v>
       </c>
-      <c r="AB5" s="7" t="s">
+      <c r="AB5" t="s">
         <v>55</v>
       </c>
       <c r="AC5" s="6">
@@ -1598,7 +2879,7 @@
       <c r="AF5" s="6">
         <v>22</v>
       </c>
-      <c r="AG5" s="7" t="s">
+      <c r="AG5" t="s">
         <v>56</v>
       </c>
       <c r="AH5" s="6">
@@ -1613,7 +2894,7 @@
       <c r="AK5" s="6">
         <v>15</v>
       </c>
-      <c r="AL5" s="7" t="s">
+      <c r="AL5" t="s">
         <v>57</v>
       </c>
       <c r="AM5" s="6">
@@ -1632,53 +2913,56 @@
         <v>750</v>
       </c>
       <c r="AR5" s="6">
-        <f>SUM(N5:AP5)</f>
-      </c>
-      <c r="AS5" s="12">
-        <f>AR5/AQ5*100</f>
-      </c>
-      <c r="AT5" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>605</v>
+      </c>
+      <c r="AS5" s="10">
+        <f t="shared" si="2"/>
+        <v>80.666666666666657</v>
+      </c>
+      <c r="AT5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6">
         <v>112237</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>38842</v>
       </c>
-      <c r="H6" s="9">
-        <f>"ABC-"&amp;B6</f>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112237</v>
+      </c>
+      <c r="I6" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="8">
         <v>43952</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L6" s="6">
         <v>1</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" t="s">
         <v>52</v>
       </c>
       <c r="N6" s="6">
@@ -1693,7 +2977,7 @@
       <c r="Q6" s="6">
         <v>19</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" t="s">
         <v>53</v>
       </c>
       <c r="S6" s="6">
@@ -1708,7 +2992,7 @@
       <c r="V6" s="6">
         <v>10</v>
       </c>
-      <c r="W6" s="7" t="s">
+      <c r="W6" t="s">
         <v>54</v>
       </c>
       <c r="X6" s="6">
@@ -1723,7 +3007,7 @@
       <c r="AA6" s="6">
         <v>20</v>
       </c>
-      <c r="AB6" s="7" t="s">
+      <c r="AB6" t="s">
         <v>55</v>
       </c>
       <c r="AC6" s="6">
@@ -1738,7 +3022,7 @@
       <c r="AF6" s="6">
         <v>20</v>
       </c>
-      <c r="AG6" s="7" t="s">
+      <c r="AG6" t="s">
         <v>56</v>
       </c>
       <c r="AH6" s="6">
@@ -1753,7 +3037,7 @@
       <c r="AK6" s="6">
         <v>10</v>
       </c>
-      <c r="AL6" s="7" t="s">
+      <c r="AL6" t="s">
         <v>57</v>
       </c>
       <c r="AM6" s="6">
@@ -1772,53 +3056,56 @@
         <v>750</v>
       </c>
       <c r="AR6" s="6">
-        <f>SUM(N6:AP6)</f>
-      </c>
-      <c r="AS6" s="12">
-        <f>AR6/AQ6*100</f>
-      </c>
-      <c r="AT6" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>513</v>
+      </c>
+      <c r="AS6" s="10">
+        <f t="shared" si="2"/>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="AT6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6">
         <v>112238</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>38843</v>
       </c>
-      <c r="H7" s="9">
-        <f>"ABC-"&amp;B7</f>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112238</v>
+      </c>
+      <c r="I7" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="8">
         <v>43952</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L7" s="6">
         <v>1</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" t="s">
         <v>52</v>
       </c>
       <c r="N7" s="6">
@@ -1833,7 +3120,7 @@
       <c r="Q7" s="6">
         <v>24</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" t="s">
         <v>53</v>
       </c>
       <c r="S7" s="6">
@@ -1848,7 +3135,7 @@
       <c r="V7" s="6">
         <v>22</v>
       </c>
-      <c r="W7" s="7" t="s">
+      <c r="W7" t="s">
         <v>54</v>
       </c>
       <c r="X7" s="6">
@@ -1863,7 +3150,7 @@
       <c r="AA7" s="6">
         <v>15</v>
       </c>
-      <c r="AB7" s="7" t="s">
+      <c r="AB7" t="s">
         <v>55</v>
       </c>
       <c r="AC7" s="6">
@@ -1878,7 +3165,7 @@
       <c r="AF7" s="6">
         <v>15</v>
       </c>
-      <c r="AG7" s="7" t="s">
+      <c r="AG7" t="s">
         <v>56</v>
       </c>
       <c r="AH7" s="6">
@@ -1893,7 +3180,7 @@
       <c r="AK7" s="6">
         <v>23</v>
       </c>
-      <c r="AL7" s="7" t="s">
+      <c r="AL7" t="s">
         <v>57</v>
       </c>
       <c r="AM7" s="6">
@@ -1912,53 +3199,56 @@
         <v>750</v>
       </c>
       <c r="AR7" s="6">
-        <f>SUM(N7:AP7)</f>
-      </c>
-      <c r="AS7" s="12">
-        <f>AR7/AQ7*100</f>
-      </c>
-      <c r="AT7" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>664</v>
+      </c>
+      <c r="AS7" s="10">
+        <f t="shared" si="2"/>
+        <v>88.533333333333331</v>
+      </c>
+      <c r="AT7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6">
         <v>112239</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>38844</v>
       </c>
-      <c r="H8" s="9">
-        <f>"ABC-"&amp;B8</f>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112239</v>
+      </c>
+      <c r="I8" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="8">
         <v>43952</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L8" s="6">
         <v>1</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" t="s">
         <v>52</v>
       </c>
       <c r="N8" s="6">
@@ -1973,7 +3263,7 @@
       <c r="Q8" s="6">
         <v>18</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="R8" t="s">
         <v>53</v>
       </c>
       <c r="S8" s="6">
@@ -1988,7 +3278,7 @@
       <c r="V8" s="6">
         <v>22</v>
       </c>
-      <c r="W8" s="7" t="s">
+      <c r="W8" t="s">
         <v>54</v>
       </c>
       <c r="X8" s="6">
@@ -2003,7 +3293,7 @@
       <c r="AA8" s="6">
         <v>23</v>
       </c>
-      <c r="AB8" s="7" t="s">
+      <c r="AB8" t="s">
         <v>55</v>
       </c>
       <c r="AC8" s="6">
@@ -2018,7 +3308,7 @@
       <c r="AF8" s="6">
         <v>10</v>
       </c>
-      <c r="AG8" s="7" t="s">
+      <c r="AG8" t="s">
         <v>56</v>
       </c>
       <c r="AH8" s="6">
@@ -2033,7 +3323,7 @@
       <c r="AK8" s="6">
         <v>22</v>
       </c>
-      <c r="AL8" s="7" t="s">
+      <c r="AL8" t="s">
         <v>57</v>
       </c>
       <c r="AM8" s="6">
@@ -2052,53 +3342,56 @@
         <v>750</v>
       </c>
       <c r="AR8" s="6">
-        <f>SUM(N8:AP8)</f>
-      </c>
-      <c r="AS8" s="12">
-        <f>AR8/AQ8*100</f>
-      </c>
-      <c r="AT8" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>616</v>
+      </c>
+      <c r="AS8" s="10">
+        <f t="shared" si="2"/>
+        <v>82.13333333333334</v>
+      </c>
+      <c r="AT8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6">
         <v>112240</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>38845</v>
       </c>
-      <c r="H9" s="9">
-        <f>"ABC-"&amp;B9</f>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112240</v>
+      </c>
+      <c r="I9" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="8">
         <v>43952</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" t="s">
         <v>52</v>
       </c>
       <c r="N9" s="6">
@@ -2113,7 +3406,7 @@
       <c r="Q9" s="6">
         <v>15</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" t="s">
         <v>53</v>
       </c>
       <c r="S9" s="6">
@@ -2128,7 +3421,7 @@
       <c r="V9" s="6">
         <v>20</v>
       </c>
-      <c r="W9" s="7" t="s">
+      <c r="W9" t="s">
         <v>54</v>
       </c>
       <c r="X9" s="6">
@@ -2143,7 +3436,7 @@
       <c r="AA9" s="6">
         <v>22</v>
       </c>
-      <c r="AB9" s="7" t="s">
+      <c r="AB9" t="s">
         <v>55</v>
       </c>
       <c r="AC9" s="6">
@@ -2158,7 +3451,7 @@
       <c r="AF9" s="6">
         <v>22</v>
       </c>
-      <c r="AG9" s="7" t="s">
+      <c r="AG9" t="s">
         <v>56</v>
       </c>
       <c r="AH9" s="6">
@@ -2173,7 +3466,7 @@
       <c r="AK9" s="6">
         <v>20</v>
       </c>
-      <c r="AL9" s="7" t="s">
+      <c r="AL9" t="s">
         <v>57</v>
       </c>
       <c r="AM9" s="6">
@@ -2192,53 +3485,56 @@
         <v>750</v>
       </c>
       <c r="AR9" s="6">
-        <f>SUM(N9:AP9)</f>
-      </c>
-      <c r="AS9" s="12">
-        <f>AR9/AQ9*100</f>
-      </c>
-      <c r="AT9" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>542</v>
+      </c>
+      <c r="AS9" s="10">
+        <f t="shared" si="2"/>
+        <v>72.266666666666666</v>
+      </c>
+      <c r="AT9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6">
         <v>112241</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>38846</v>
       </c>
-      <c r="H10" s="9">
-        <f>"ABC-"&amp;B10</f>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112241</v>
+      </c>
+      <c r="I10" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="8">
         <v>43952</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L10" s="6">
         <v>1</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" t="s">
         <v>52</v>
       </c>
       <c r="N10" s="6">
@@ -2253,7 +3549,7 @@
       <c r="Q10" s="6">
         <v>23</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" t="s">
         <v>53</v>
       </c>
       <c r="S10" s="6">
@@ -2268,7 +3564,7 @@
       <c r="V10" s="6">
         <v>15</v>
       </c>
-      <c r="W10" s="7" t="s">
+      <c r="W10" t="s">
         <v>54</v>
       </c>
       <c r="X10" s="6">
@@ -2283,7 +3579,7 @@
       <c r="AA10" s="6">
         <v>20</v>
       </c>
-      <c r="AB10" s="7" t="s">
+      <c r="AB10" t="s">
         <v>55</v>
       </c>
       <c r="AC10" s="6">
@@ -2298,7 +3594,7 @@
       <c r="AF10" s="6">
         <v>15</v>
       </c>
-      <c r="AG10" s="7" t="s">
+      <c r="AG10" t="s">
         <v>56</v>
       </c>
       <c r="AH10" s="6">
@@ -2313,7 +3609,7 @@
       <c r="AK10" s="6">
         <v>15</v>
       </c>
-      <c r="AL10" s="7" t="s">
+      <c r="AL10" t="s">
         <v>57</v>
       </c>
       <c r="AM10" s="6">
@@ -2332,53 +3628,56 @@
         <v>750</v>
       </c>
       <c r="AR10" s="6">
-        <f>SUM(N10:AP10)</f>
-      </c>
-      <c r="AS10" s="12">
-        <f>AR10/AQ10*100</f>
-      </c>
-      <c r="AT10" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>594</v>
+      </c>
+      <c r="AS10" s="10">
+        <f t="shared" si="2"/>
+        <v>79.2</v>
+      </c>
+      <c r="AT10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="6">
         <v>112242</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>38847</v>
       </c>
-      <c r="H11" s="9">
-        <f>"ABC-"&amp;B11</f>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112242</v>
+      </c>
+      <c r="I11" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="8">
         <v>43952</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L11" s="6">
         <v>1</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" t="s">
         <v>52</v>
       </c>
       <c r="N11" s="6">
@@ -2393,7 +3692,7 @@
       <c r="Q11" s="6">
         <v>10</v>
       </c>
-      <c r="R11" s="7" t="s">
+      <c r="R11" t="s">
         <v>53</v>
       </c>
       <c r="S11" s="6">
@@ -2408,7 +3707,7 @@
       <c r="V11" s="6">
         <v>23</v>
       </c>
-      <c r="W11" s="7" t="s">
+      <c r="W11" t="s">
         <v>54</v>
       </c>
       <c r="X11" s="6">
@@ -2423,7 +3722,7 @@
       <c r="AA11" s="6">
         <v>15</v>
       </c>
-      <c r="AB11" s="7" t="s">
+      <c r="AB11" t="s">
         <v>55</v>
       </c>
       <c r="AC11" s="6">
@@ -2438,7 +3737,7 @@
       <c r="AF11" s="6">
         <v>10</v>
       </c>
-      <c r="AG11" s="7" t="s">
+      <c r="AG11" t="s">
         <v>56</v>
       </c>
       <c r="AH11" s="6">
@@ -2453,7 +3752,7 @@
       <c r="AK11" s="6">
         <v>10</v>
       </c>
-      <c r="AL11" s="7" t="s">
+      <c r="AL11" t="s">
         <v>57</v>
       </c>
       <c r="AM11" s="6">
@@ -2472,53 +3771,56 @@
         <v>750</v>
       </c>
       <c r="AR11" s="6">
-        <f>SUM(N11:AP11)</f>
-      </c>
-      <c r="AS11" s="12">
-        <f>AR11/AQ11*100</f>
-      </c>
-      <c r="AT11" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>646</v>
+      </c>
+      <c r="AS11" s="10">
+        <f t="shared" si="2"/>
+        <v>86.133333333333326</v>
+      </c>
+      <c r="AT11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="6">
         <v>112243</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>38848</v>
       </c>
-      <c r="H12" s="9">
-        <f>"ABC-"&amp;B12</f>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112243</v>
+      </c>
+      <c r="I12" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="8">
         <v>43952</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L12" s="6">
         <v>1</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" t="s">
         <v>52</v>
       </c>
       <c r="N12" s="6">
@@ -2533,7 +3835,7 @@
       <c r="Q12" s="6">
         <v>22</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" t="s">
         <v>53</v>
       </c>
       <c r="S12" s="6">
@@ -2548,7 +3850,7 @@
       <c r="V12" s="6">
         <v>10</v>
       </c>
-      <c r="W12" s="7" t="s">
+      <c r="W12" t="s">
         <v>54</v>
       </c>
       <c r="X12" s="6">
@@ -2563,7 +3865,7 @@
       <c r="AA12" s="6">
         <v>10</v>
       </c>
-      <c r="AB12" s="7" t="s">
+      <c r="AB12" t="s">
         <v>55</v>
       </c>
       <c r="AC12" s="6">
@@ -2578,7 +3880,7 @@
       <c r="AF12" s="6">
         <v>23</v>
       </c>
-      <c r="AG12" s="7" t="s">
+      <c r="AG12" t="s">
         <v>56</v>
       </c>
       <c r="AH12" s="6">
@@ -2593,7 +3895,7 @@
       <c r="AK12" s="6">
         <v>10</v>
       </c>
-      <c r="AL12" s="7" t="s">
+      <c r="AL12" t="s">
         <v>57</v>
       </c>
       <c r="AM12" s="6">
@@ -2612,53 +3914,56 @@
         <v>750</v>
       </c>
       <c r="AR12" s="6">
-        <f>SUM(N12:AP12)</f>
-      </c>
-      <c r="AS12" s="12">
-        <f>AR12/AQ12*100</f>
-      </c>
-      <c r="AT12" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>663</v>
+      </c>
+      <c r="AS12" s="10">
+        <f t="shared" si="2"/>
+        <v>88.4</v>
+      </c>
+      <c r="AT12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="6">
         <v>112244</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>38849</v>
       </c>
-      <c r="H13" s="9">
-        <f>"ABC-"&amp;B13</f>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112244</v>
+      </c>
+      <c r="I13" t="s">
         <v>50</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="8">
         <v>43952</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L13" s="6">
         <v>1</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" t="s">
         <v>52</v>
       </c>
       <c r="N13" s="6">
@@ -2673,7 +3978,7 @@
       <c r="Q13" s="6">
         <v>22</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="R13" t="s">
         <v>53</v>
       </c>
       <c r="S13" s="6">
@@ -2688,7 +3993,7 @@
       <c r="V13" s="6">
         <v>22</v>
       </c>
-      <c r="W13" s="7" t="s">
+      <c r="W13" t="s">
         <v>54</v>
       </c>
       <c r="X13" s="6">
@@ -2703,7 +4008,7 @@
       <c r="AA13" s="6">
         <v>22</v>
       </c>
-      <c r="AB13" s="7" t="s">
+      <c r="AB13" t="s">
         <v>55</v>
       </c>
       <c r="AC13" s="6">
@@ -2718,7 +4023,7 @@
       <c r="AF13" s="6">
         <v>22</v>
       </c>
-      <c r="AG13" s="7" t="s">
+      <c r="AG13" t="s">
         <v>56</v>
       </c>
       <c r="AH13" s="6">
@@ -2733,7 +4038,7 @@
       <c r="AK13" s="6">
         <v>23</v>
       </c>
-      <c r="AL13" s="7" t="s">
+      <c r="AL13" t="s">
         <v>57</v>
       </c>
       <c r="AM13" s="6">
@@ -2752,53 +4057,56 @@
         <v>750</v>
       </c>
       <c r="AR13" s="6">
-        <f>SUM(N13:AP13)</f>
-      </c>
-      <c r="AS13" s="12">
-        <f>AR13/AQ13*100</f>
-      </c>
-      <c r="AT13" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>588</v>
+      </c>
+      <c r="AS13" s="10">
+        <f t="shared" si="2"/>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="AT13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6">
         <v>112245</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>38850</v>
       </c>
-      <c r="H14" s="9">
-        <f>"ABC-"&amp;B14</f>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112245</v>
+      </c>
+      <c r="I14" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="8">
         <v>43952</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L14" s="6">
         <v>1</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" t="s">
         <v>52</v>
       </c>
       <c r="N14" s="6">
@@ -2813,7 +4121,7 @@
       <c r="Q14" s="6">
         <v>20</v>
       </c>
-      <c r="R14" s="7" t="s">
+      <c r="R14" t="s">
         <v>53</v>
       </c>
       <c r="S14" s="6">
@@ -2828,7 +4136,7 @@
       <c r="V14" s="6">
         <v>23</v>
       </c>
-      <c r="W14" s="7" t="s">
+      <c r="W14" t="s">
         <v>54</v>
       </c>
       <c r="X14" s="6">
@@ -2843,7 +4151,7 @@
       <c r="AA14" s="6">
         <v>22</v>
       </c>
-      <c r="AB14" s="7" t="s">
+      <c r="AB14" t="s">
         <v>55</v>
       </c>
       <c r="AC14" s="6">
@@ -2858,7 +4166,7 @@
       <c r="AF14" s="6">
         <v>20</v>
       </c>
-      <c r="AG14" s="7" t="s">
+      <c r="AG14" t="s">
         <v>56</v>
       </c>
       <c r="AH14" s="6">
@@ -2873,7 +4181,7 @@
       <c r="AK14" s="6">
         <v>22</v>
       </c>
-      <c r="AL14" s="7" t="s">
+      <c r="AL14" t="s">
         <v>57</v>
       </c>
       <c r="AM14" s="6">
@@ -2892,53 +4200,56 @@
         <v>750</v>
       </c>
       <c r="AR14" s="6">
-        <f>SUM(N14:AP14)</f>
-      </c>
-      <c r="AS14" s="12">
-        <f>AR14/AQ14*100</f>
-      </c>
-      <c r="AT14" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>546</v>
+      </c>
+      <c r="AS14" s="10">
+        <f t="shared" si="2"/>
+        <v>72.8</v>
+      </c>
+      <c r="AT14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="6">
         <v>112246</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <v>38851</v>
       </c>
-      <c r="H15" s="9">
-        <f>"ABC-"&amp;B15</f>
-      </c>
-      <c r="I15" s="7" t="s">
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112246</v>
+      </c>
+      <c r="I15" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="8">
         <v>43952</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L15" s="6">
         <v>1</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" t="s">
         <v>52</v>
       </c>
       <c r="N15" s="6">
@@ -2953,7 +4264,7 @@
       <c r="Q15" s="6">
         <v>17</v>
       </c>
-      <c r="R15" s="7" t="s">
+      <c r="R15" t="s">
         <v>53</v>
       </c>
       <c r="S15" s="6">
@@ -2968,7 +4279,7 @@
       <c r="V15" s="6">
         <v>24</v>
       </c>
-      <c r="W15" s="7" t="s">
+      <c r="W15" t="s">
         <v>54</v>
       </c>
       <c r="X15" s="6">
@@ -2983,7 +4294,7 @@
       <c r="AA15" s="6">
         <v>23</v>
       </c>
-      <c r="AB15" s="7" t="s">
+      <c r="AB15" t="s">
         <v>55</v>
       </c>
       <c r="AC15" s="6">
@@ -2998,7 +4309,7 @@
       <c r="AF15" s="6">
         <v>20</v>
       </c>
-      <c r="AG15" s="7" t="s">
+      <c r="AG15" t="s">
         <v>56</v>
       </c>
       <c r="AH15" s="6">
@@ -3013,7 +4324,7 @@
       <c r="AK15" s="6">
         <v>15</v>
       </c>
-      <c r="AL15" s="7" t="s">
+      <c r="AL15" t="s">
         <v>57</v>
       </c>
       <c r="AM15" s="6">
@@ -3032,53 +4343,56 @@
         <v>750</v>
       </c>
       <c r="AR15" s="6">
-        <f>SUM(N15:AP15)</f>
-      </c>
-      <c r="AS15" s="12">
-        <f>AR15/AQ15*100</f>
-      </c>
-      <c r="AT15" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>618</v>
+      </c>
+      <c r="AS15" s="10">
+        <f t="shared" si="2"/>
+        <v>82.399999999999991</v>
+      </c>
+      <c r="AT15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="6">
         <v>112247</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>38852</v>
       </c>
-      <c r="H16" s="9">
-        <f>"ABC-"&amp;B16</f>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112247</v>
+      </c>
+      <c r="I16" t="s">
         <v>50</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="8">
         <v>43952</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L16" s="6">
         <v>1</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" t="s">
         <v>52</v>
       </c>
       <c r="N16" s="6">
@@ -3093,7 +4407,7 @@
       <c r="Q16" s="6">
         <v>20</v>
       </c>
-      <c r="R16" s="7" t="s">
+      <c r="R16" t="s">
         <v>53</v>
       </c>
       <c r="S16" s="6">
@@ -3108,7 +4422,7 @@
       <c r="V16" s="6">
         <v>18</v>
       </c>
-      <c r="W16" s="7" t="s">
+      <c r="W16" t="s">
         <v>54</v>
       </c>
       <c r="X16" s="6">
@@ -3123,7 +4437,7 @@
       <c r="AA16" s="6">
         <v>10</v>
       </c>
-      <c r="AB16" s="7" t="s">
+      <c r="AB16" t="s">
         <v>55</v>
       </c>
       <c r="AC16" s="6">
@@ -3138,7 +4452,7 @@
       <c r="AF16" s="6">
         <v>15</v>
       </c>
-      <c r="AG16" s="7" t="s">
+      <c r="AG16" t="s">
         <v>56</v>
       </c>
       <c r="AH16" s="6">
@@ -3153,7 +4467,7 @@
       <c r="AK16" s="6">
         <v>10</v>
       </c>
-      <c r="AL16" s="7" t="s">
+      <c r="AL16" t="s">
         <v>57</v>
       </c>
       <c r="AM16" s="6">
@@ -3172,53 +4486,56 @@
         <v>750</v>
       </c>
       <c r="AR16" s="6">
-        <f>SUM(N16:AP16)</f>
-      </c>
-      <c r="AS16" s="12">
-        <f>AR16/AQ16*100</f>
-      </c>
-      <c r="AT16" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>567</v>
+      </c>
+      <c r="AS16" s="10">
+        <f t="shared" si="2"/>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AT16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="6">
         <v>112248</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" t="s">
         <v>118</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>38853</v>
       </c>
-      <c r="H17" s="9">
-        <f>"ABC-"&amp;B17</f>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112248</v>
+      </c>
+      <c r="I17" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="8">
         <v>43952</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L17" s="6">
         <v>1</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" t="s">
         <v>52</v>
       </c>
       <c r="N17" s="6">
@@ -3233,7 +4550,7 @@
       <c r="Q17" s="6">
         <v>23</v>
       </c>
-      <c r="R17" s="7" t="s">
+      <c r="R17" t="s">
         <v>53</v>
       </c>
       <c r="S17" s="6">
@@ -3248,7 +4565,7 @@
       <c r="V17" s="6">
         <v>15</v>
       </c>
-      <c r="W17" s="7" t="s">
+      <c r="W17" t="s">
         <v>54</v>
       </c>
       <c r="X17" s="6">
@@ -3263,7 +4580,7 @@
       <c r="AA17" s="6">
         <v>22</v>
       </c>
-      <c r="AB17" s="7" t="s">
+      <c r="AB17" t="s">
         <v>55</v>
       </c>
       <c r="AC17" s="6">
@@ -3278,7 +4595,7 @@
       <c r="AF17" s="6">
         <v>23</v>
       </c>
-      <c r="AG17" s="7" t="s">
+      <c r="AG17" t="s">
         <v>56</v>
       </c>
       <c r="AH17" s="6">
@@ -3293,7 +4610,7 @@
       <c r="AK17" s="6">
         <v>22</v>
       </c>
-      <c r="AL17" s="7" t="s">
+      <c r="AL17" t="s">
         <v>57</v>
       </c>
       <c r="AM17" s="6">
@@ -3312,53 +4629,56 @@
         <v>750</v>
       </c>
       <c r="AR17" s="6">
-        <f>SUM(N17:AP17)</f>
-      </c>
-      <c r="AS17" s="12">
-        <f>AR17/AQ17*100</f>
-      </c>
-      <c r="AT17" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="AS17" s="10">
+        <f t="shared" si="2"/>
+        <v>85.333333333333343</v>
+      </c>
+      <c r="AT17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="6">
         <v>112249</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>38854</v>
       </c>
-      <c r="H18" s="9">
-        <f>"ABC-"&amp;B18</f>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112249</v>
+      </c>
+      <c r="I18" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="8">
         <v>43952</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L18" s="6">
         <v>1</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="M18" t="s">
         <v>52</v>
       </c>
       <c r="N18" s="6">
@@ -3373,7 +4693,7 @@
       <c r="Q18" s="6">
         <v>22</v>
       </c>
-      <c r="R18" s="7" t="s">
+      <c r="R18" t="s">
         <v>53</v>
       </c>
       <c r="S18" s="6">
@@ -3388,7 +4708,7 @@
       <c r="V18" s="6">
         <v>23</v>
       </c>
-      <c r="W18" s="7" t="s">
+      <c r="W18" t="s">
         <v>54</v>
       </c>
       <c r="X18" s="6">
@@ -3403,7 +4723,7 @@
       <c r="AA18" s="6">
         <v>22</v>
       </c>
-      <c r="AB18" s="7" t="s">
+      <c r="AB18" t="s">
         <v>55</v>
       </c>
       <c r="AC18" s="6">
@@ -3418,7 +4738,7 @@
       <c r="AF18" s="6">
         <v>22</v>
       </c>
-      <c r="AG18" s="7" t="s">
+      <c r="AG18" t="s">
         <v>56</v>
       </c>
       <c r="AH18" s="6">
@@ -3433,7 +4753,7 @@
       <c r="AK18" s="6">
         <v>15</v>
       </c>
-      <c r="AL18" s="7" t="s">
+      <c r="AL18" t="s">
         <v>57</v>
       </c>
       <c r="AM18" s="6">
@@ -3452,53 +4772,56 @@
         <v>750</v>
       </c>
       <c r="AR18" s="6">
-        <f>SUM(N18:AP18)</f>
-      </c>
-      <c r="AS18" s="12">
-        <f>AR18/AQ18*100</f>
-      </c>
-      <c r="AT18" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>605</v>
+      </c>
+      <c r="AS18" s="10">
+        <f t="shared" si="2"/>
+        <v>80.666666666666657</v>
+      </c>
+      <c r="AT18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="6">
         <v>112250</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" t="s">
         <v>125</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>38855</v>
       </c>
-      <c r="H19" s="9">
-        <f>"ABC-"&amp;B19</f>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112250</v>
+      </c>
+      <c r="I19" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="8">
         <v>43952</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L19" s="6">
         <v>1</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="M19" t="s">
         <v>52</v>
       </c>
       <c r="N19" s="6">
@@ -3513,7 +4836,7 @@
       <c r="Q19" s="6">
         <v>19</v>
       </c>
-      <c r="R19" s="7" t="s">
+      <c r="R19" t="s">
         <v>53</v>
       </c>
       <c r="S19" s="6">
@@ -3528,7 +4851,7 @@
       <c r="V19" s="6">
         <v>10</v>
       </c>
-      <c r="W19" s="7" t="s">
+      <c r="W19" t="s">
         <v>54</v>
       </c>
       <c r="X19" s="6">
@@ -3543,7 +4866,7 @@
       <c r="AA19" s="6">
         <v>20</v>
       </c>
-      <c r="AB19" s="7" t="s">
+      <c r="AB19" t="s">
         <v>55</v>
       </c>
       <c r="AC19" s="6">
@@ -3558,7 +4881,7 @@
       <c r="AF19" s="6">
         <v>20</v>
       </c>
-      <c r="AG19" s="7" t="s">
+      <c r="AG19" t="s">
         <v>56</v>
       </c>
       <c r="AH19" s="6">
@@ -3573,7 +4896,7 @@
       <c r="AK19" s="6">
         <v>10</v>
       </c>
-      <c r="AL19" s="7" t="s">
+      <c r="AL19" t="s">
         <v>57</v>
       </c>
       <c r="AM19" s="6">
@@ -3592,53 +4915,56 @@
         <v>750</v>
       </c>
       <c r="AR19" s="6">
-        <f>SUM(N19:AP19)</f>
-      </c>
-      <c r="AS19" s="12">
-        <f>AR19/AQ19*100</f>
-      </c>
-      <c r="AT19" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>513</v>
+      </c>
+      <c r="AS19" s="10">
+        <f t="shared" si="2"/>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="AT19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="6">
         <v>112251</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" t="s">
         <v>130</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="7">
         <v>38856</v>
       </c>
-      <c r="H20" s="9">
-        <f>"ABC-"&amp;B20</f>
-      </c>
-      <c r="I20" s="7" t="s">
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112251</v>
+      </c>
+      <c r="I20" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="8">
         <v>43952</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L20" s="6">
         <v>1</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" t="s">
         <v>52</v>
       </c>
       <c r="N20" s="6">
@@ -3653,7 +4979,7 @@
       <c r="Q20" s="6">
         <v>24</v>
       </c>
-      <c r="R20" s="7" t="s">
+      <c r="R20" t="s">
         <v>53</v>
       </c>
       <c r="S20" s="6">
@@ -3668,7 +4994,7 @@
       <c r="V20" s="6">
         <v>22</v>
       </c>
-      <c r="W20" s="7" t="s">
+      <c r="W20" t="s">
         <v>54</v>
       </c>
       <c r="X20" s="6">
@@ -3683,7 +5009,7 @@
       <c r="AA20" s="6">
         <v>15</v>
       </c>
-      <c r="AB20" s="7" t="s">
+      <c r="AB20" t="s">
         <v>55</v>
       </c>
       <c r="AC20" s="6">
@@ -3698,7 +5024,7 @@
       <c r="AF20" s="6">
         <v>15</v>
       </c>
-      <c r="AG20" s="7" t="s">
+      <c r="AG20" t="s">
         <v>56</v>
       </c>
       <c r="AH20" s="6">
@@ -3713,7 +5039,7 @@
       <c r="AK20" s="6">
         <v>23</v>
       </c>
-      <c r="AL20" s="7" t="s">
+      <c r="AL20" t="s">
         <v>57</v>
       </c>
       <c r="AM20" s="6">
@@ -3732,53 +5058,56 @@
         <v>750</v>
       </c>
       <c r="AR20" s="6">
-        <f>SUM(N20:AP20)</f>
-      </c>
-      <c r="AS20" s="12">
-        <f>AR20/AQ20*100</f>
-      </c>
-      <c r="AT20" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>664</v>
+      </c>
+      <c r="AS20" s="10">
+        <f t="shared" si="2"/>
+        <v>88.533333333333331</v>
+      </c>
+      <c r="AT20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="6">
         <v>112252</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" t="s">
         <v>133</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="7">
         <v>38857</v>
       </c>
-      <c r="H21" s="9">
-        <f>"ABC-"&amp;B21</f>
-      </c>
-      <c r="I21" s="7" t="s">
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112252</v>
+      </c>
+      <c r="I21" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="8">
         <v>43952</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L21" s="6">
         <v>1</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="M21" t="s">
         <v>52</v>
       </c>
       <c r="N21" s="6">
@@ -3793,7 +5122,7 @@
       <c r="Q21" s="6">
         <v>18</v>
       </c>
-      <c r="R21" s="7" t="s">
+      <c r="R21" t="s">
         <v>53</v>
       </c>
       <c r="S21" s="6">
@@ -3808,7 +5137,7 @@
       <c r="V21" s="6">
         <v>22</v>
       </c>
-      <c r="W21" s="7" t="s">
+      <c r="W21" t="s">
         <v>54</v>
       </c>
       <c r="X21" s="6">
@@ -3823,7 +5152,7 @@
       <c r="AA21" s="6">
         <v>23</v>
       </c>
-      <c r="AB21" s="7" t="s">
+      <c r="AB21" t="s">
         <v>55</v>
       </c>
       <c r="AC21" s="6">
@@ -3838,7 +5167,7 @@
       <c r="AF21" s="6">
         <v>10</v>
       </c>
-      <c r="AG21" s="7" t="s">
+      <c r="AG21" t="s">
         <v>56</v>
       </c>
       <c r="AH21" s="6">
@@ -3853,7 +5182,7 @@
       <c r="AK21" s="6">
         <v>22</v>
       </c>
-      <c r="AL21" s="7" t="s">
+      <c r="AL21" t="s">
         <v>57</v>
       </c>
       <c r="AM21" s="6">
@@ -3872,53 +5201,56 @@
         <v>750</v>
       </c>
       <c r="AR21" s="6">
-        <f>SUM(N21:AP21)</f>
-      </c>
-      <c r="AS21" s="12">
-        <f>AR21/AQ21*100</f>
-      </c>
-      <c r="AT21" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>616</v>
+      </c>
+      <c r="AS21" s="10">
+        <f t="shared" si="2"/>
+        <v>82.13333333333334</v>
+      </c>
+      <c r="AT21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="6">
         <v>112253</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" t="s">
         <v>136</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" t="s">
         <v>137</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" t="s">
         <v>138</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>38858</v>
       </c>
-      <c r="H22" s="9">
-        <f>"ABC-"&amp;B22</f>
-      </c>
-      <c r="I22" s="7" t="s">
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112253</v>
+      </c>
+      <c r="I22" t="s">
         <v>50</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="8">
         <v>43952</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L22" s="6">
         <v>1</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" t="s">
         <v>52</v>
       </c>
       <c r="N22" s="6">
@@ -3933,7 +5265,7 @@
       <c r="Q22" s="6">
         <v>15</v>
       </c>
-      <c r="R22" s="7" t="s">
+      <c r="R22" t="s">
         <v>53</v>
       </c>
       <c r="S22" s="6">
@@ -3948,7 +5280,7 @@
       <c r="V22" s="6">
         <v>20</v>
       </c>
-      <c r="W22" s="7" t="s">
+      <c r="W22" t="s">
         <v>54</v>
       </c>
       <c r="X22" s="6">
@@ -3963,7 +5295,7 @@
       <c r="AA22" s="6">
         <v>22</v>
       </c>
-      <c r="AB22" s="7" t="s">
+      <c r="AB22" t="s">
         <v>55</v>
       </c>
       <c r="AC22" s="6">
@@ -3978,7 +5310,7 @@
       <c r="AF22" s="6">
         <v>22</v>
       </c>
-      <c r="AG22" s="7" t="s">
+      <c r="AG22" t="s">
         <v>56</v>
       </c>
       <c r="AH22" s="6">
@@ -3993,7 +5325,7 @@
       <c r="AK22" s="6">
         <v>20</v>
       </c>
-      <c r="AL22" s="7" t="s">
+      <c r="AL22" t="s">
         <v>57</v>
       </c>
       <c r="AM22" s="6">
@@ -4012,53 +5344,56 @@
         <v>750</v>
       </c>
       <c r="AR22" s="6">
-        <f>SUM(N22:AP22)</f>
-      </c>
-      <c r="AS22" s="12">
-        <f>AR22/AQ22*100</f>
-      </c>
-      <c r="AT22" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>542</v>
+      </c>
+      <c r="AS22" s="10">
+        <f t="shared" si="2"/>
+        <v>72.266666666666666</v>
+      </c>
+      <c r="AT22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6">
         <v>112254</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>139</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" t="s">
         <v>141</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" t="s">
         <v>142</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <v>38859</v>
       </c>
-      <c r="H23" s="9">
-        <f>"ABC-"&amp;B23</f>
-      </c>
-      <c r="I23" s="7" t="s">
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112254</v>
+      </c>
+      <c r="I23" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="8">
         <v>43952</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L23" s="6">
         <v>1</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="M23" t="s">
         <v>52</v>
       </c>
       <c r="N23" s="6">
@@ -4073,7 +5408,7 @@
       <c r="Q23" s="6">
         <v>23</v>
       </c>
-      <c r="R23" s="7" t="s">
+      <c r="R23" t="s">
         <v>53</v>
       </c>
       <c r="S23" s="6">
@@ -4088,7 +5423,7 @@
       <c r="V23" s="6">
         <v>15</v>
       </c>
-      <c r="W23" s="7" t="s">
+      <c r="W23" t="s">
         <v>54</v>
       </c>
       <c r="X23" s="6">
@@ -4103,7 +5438,7 @@
       <c r="AA23" s="6">
         <v>20</v>
       </c>
-      <c r="AB23" s="7" t="s">
+      <c r="AB23" t="s">
         <v>55</v>
       </c>
       <c r="AC23" s="6">
@@ -4118,7 +5453,7 @@
       <c r="AF23" s="6">
         <v>15</v>
       </c>
-      <c r="AG23" s="7" t="s">
+      <c r="AG23" t="s">
         <v>56</v>
       </c>
       <c r="AH23" s="6">
@@ -4133,7 +5468,7 @@
       <c r="AK23" s="6">
         <v>15</v>
       </c>
-      <c r="AL23" s="7" t="s">
+      <c r="AL23" t="s">
         <v>57</v>
       </c>
       <c r="AM23" s="6">
@@ -4152,53 +5487,56 @@
         <v>750</v>
       </c>
       <c r="AR23" s="6">
-        <f>SUM(N23:AP23)</f>
-      </c>
-      <c r="AS23" s="12">
-        <f>AR23/AQ23*100</f>
-      </c>
-      <c r="AT23" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>594</v>
+      </c>
+      <c r="AS23" s="10">
+        <f t="shared" si="2"/>
+        <v>79.2</v>
+      </c>
+      <c r="AT23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="6">
         <v>112255</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" t="s">
         <v>146</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="7">
         <v>38860</v>
       </c>
-      <c r="H24" s="9">
-        <f>"ABC-"&amp;B24</f>
-      </c>
-      <c r="I24" s="7" t="s">
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112255</v>
+      </c>
+      <c r="I24" t="s">
         <v>50</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="8">
         <v>43952</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L24" s="6">
         <v>1</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="M24" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="6">
@@ -4213,7 +5551,7 @@
       <c r="Q24" s="6">
         <v>10</v>
       </c>
-      <c r="R24" s="7" t="s">
+      <c r="R24" t="s">
         <v>53</v>
       </c>
       <c r="S24" s="6">
@@ -4228,7 +5566,7 @@
       <c r="V24" s="6">
         <v>23</v>
       </c>
-      <c r="W24" s="7" t="s">
+      <c r="W24" t="s">
         <v>54</v>
       </c>
       <c r="X24" s="6">
@@ -4243,7 +5581,7 @@
       <c r="AA24" s="6">
         <v>15</v>
       </c>
-      <c r="AB24" s="7" t="s">
+      <c r="AB24" t="s">
         <v>55</v>
       </c>
       <c r="AC24" s="6">
@@ -4258,7 +5596,7 @@
       <c r="AF24" s="6">
         <v>10</v>
       </c>
-      <c r="AG24" s="7" t="s">
+      <c r="AG24" t="s">
         <v>56</v>
       </c>
       <c r="AH24" s="6">
@@ -4273,7 +5611,7 @@
       <c r="AK24" s="6">
         <v>10</v>
       </c>
-      <c r="AL24" s="7" t="s">
+      <c r="AL24" t="s">
         <v>57</v>
       </c>
       <c r="AM24" s="6">
@@ -4292,53 +5630,56 @@
         <v>750</v>
       </c>
       <c r="AR24" s="6">
-        <f>SUM(N24:AP24)</f>
-      </c>
-      <c r="AS24" s="12">
-        <f>AR24/AQ24*100</f>
-      </c>
-      <c r="AT24" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>646</v>
+      </c>
+      <c r="AS24" s="10">
+        <f t="shared" si="2"/>
+        <v>86.133333333333326</v>
+      </c>
+      <c r="AT24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="6">
         <v>112256</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" t="s">
         <v>148</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>38861</v>
       </c>
-      <c r="H25" s="9">
-        <f>"ABC-"&amp;B25</f>
-      </c>
-      <c r="I25" s="7" t="s">
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112256</v>
+      </c>
+      <c r="I25" t="s">
         <v>50</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="8">
         <v>43952</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L25" s="6">
         <v>1</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="M25" t="s">
         <v>52</v>
       </c>
       <c r="N25" s="6">
@@ -4353,7 +5694,7 @@
       <c r="Q25" s="6">
         <v>22</v>
       </c>
-      <c r="R25" s="7" t="s">
+      <c r="R25" t="s">
         <v>53</v>
       </c>
       <c r="S25" s="6">
@@ -4368,7 +5709,7 @@
       <c r="V25" s="6">
         <v>10</v>
       </c>
-      <c r="W25" s="7" t="s">
+      <c r="W25" t="s">
         <v>54</v>
       </c>
       <c r="X25" s="6">
@@ -4383,7 +5724,7 @@
       <c r="AA25" s="6">
         <v>10</v>
       </c>
-      <c r="AB25" s="7" t="s">
+      <c r="AB25" t="s">
         <v>55</v>
       </c>
       <c r="AC25" s="6">
@@ -4398,7 +5739,7 @@
       <c r="AF25" s="6">
         <v>23</v>
       </c>
-      <c r="AG25" s="7" t="s">
+      <c r="AG25" t="s">
         <v>56</v>
       </c>
       <c r="AH25" s="6">
@@ -4413,7 +5754,7 @@
       <c r="AK25" s="6">
         <v>10</v>
       </c>
-      <c r="AL25" s="7" t="s">
+      <c r="AL25" t="s">
         <v>57</v>
       </c>
       <c r="AM25" s="6">
@@ -4432,53 +5773,56 @@
         <v>750</v>
       </c>
       <c r="AR25" s="6">
-        <f>SUM(N25:AP25)</f>
-      </c>
-      <c r="AS25" s="12">
-        <f>AR25/AQ25*100</f>
-      </c>
-      <c r="AT25" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>663</v>
+      </c>
+      <c r="AS25" s="10">
+        <f t="shared" si="2"/>
+        <v>88.4</v>
+      </c>
+      <c r="AT25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>25</v>
       </c>
       <c r="B26" s="6">
         <v>112257</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" t="s">
         <v>153</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" t="s">
         <v>154</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="7">
         <v>38862</v>
       </c>
-      <c r="H26" s="9">
-        <f>"ABC-"&amp;B26</f>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>ABC-112257</v>
+      </c>
+      <c r="I26" t="s">
         <v>50</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="8">
         <v>43952</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="9" t="s">
         <v>51</v>
       </c>
       <c r="L26" s="6">
         <v>1</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="M26" t="s">
         <v>52</v>
       </c>
       <c r="N26" s="6">
@@ -4493,7 +5837,7 @@
       <c r="Q26" s="6">
         <v>22</v>
       </c>
-      <c r="R26" s="7" t="s">
+      <c r="R26" t="s">
         <v>53</v>
       </c>
       <c r="S26" s="6">
@@ -4508,7 +5852,7 @@
       <c r="V26" s="6">
         <v>22</v>
       </c>
-      <c r="W26" s="7" t="s">
+      <c r="W26" t="s">
         <v>54</v>
       </c>
       <c r="X26" s="6">
@@ -4523,7 +5867,7 @@
       <c r="AA26" s="6">
         <v>22</v>
       </c>
-      <c r="AB26" s="7" t="s">
+      <c r="AB26" t="s">
         <v>55</v>
       </c>
       <c r="AC26" s="6">
@@ -4538,7 +5882,7 @@
       <c r="AF26" s="6">
         <v>22</v>
       </c>
-      <c r="AG26" s="7" t="s">
+      <c r="AG26" t="s">
         <v>56</v>
       </c>
       <c r="AH26" s="6">
@@ -4553,7 +5897,7 @@
       <c r="AK26" s="6">
         <v>23</v>
       </c>
-      <c r="AL26" s="7" t="s">
+      <c r="AL26" t="s">
         <v>57</v>
       </c>
       <c r="AM26" s="6">
@@ -4572,16 +5916,19 @@
         <v>750</v>
       </c>
       <c r="AR26" s="6">
-        <f>SUM(N26:AP26)</f>
-      </c>
-      <c r="AS26" s="12">
-        <f>AR26/AQ26*100</f>
-      </c>
-      <c r="AT26" s="7" t="s">
+        <f t="shared" si="1"/>
+        <v>588</v>
+      </c>
+      <c r="AS26" s="10">
+        <f t="shared" si="2"/>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="AT26" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FCD56-ED9A-4709-8E48-54BDEC2B27DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973E8D79-C463-4F2C-AD41-3FDAE6C9C320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -593,9 +593,6 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2348,7 +2345,7 @@
       <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="15" t="s">
+      <c r="AU1" s="1" t="s">
         <v>155</v>
       </c>
     </row>

--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECC079B-ECAA-4163-8AB4-7D23B15842D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DA9F2C-0FB6-4B44-8A07-393A0C88CE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEM-1" sheetId="1" r:id="rId1"/>

--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB8F82-AF0D-47B0-8DA5-3B8A2AD3371C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA42EF4F-2F7D-45BE-9FC6-8E3853748973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -971,7 +971,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>

--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB0BE3-DED2-4DFC-96CF-3653630911EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDBBC5F-AC18-4DC7-AAE7-E8DAA6EF0596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/sample_data_generator/sample_data/sample.xlsx
+++ b/sample_data_generator/sample_data/sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\omnissiah\Project\nodejs\react\Smart_Data_Management\sample_data_generator\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4203EAF7-0577-495D-9B22-8B683F64353A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20FB17C-6781-481E-9BA2-1AF954767574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="196">
   <si>
     <t>Exam_SEAT_NO</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>Profile_Image</t>
+  </si>
+  <si>
+    <t>Signature</t>
   </si>
 </sst>
 </file>
@@ -674,12 +677,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1832,6 +1838,1136 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>2381149</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1341120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2A0EA9D-E276-354E-B315-CAE128455014}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB229BBA-AAD3-4397-813D-8FE1DCA34353}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7800DB8B-B12E-4556-9CDD-966F49C12634}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 109">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A040A7CB-13B5-49B6-B9AF-B391E695EAED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{057CDE2D-AB54-4C81-A443-5869AE11CBA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEE1EBD4-91BC-4128-A9EA-51175291671C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FB65AD4-E702-4FDA-91D4-34FBAB1C963D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C71C208-52E1-487D-A868-47FB397E3D1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C5C4467-6426-459F-81F1-433547E7E5BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A91DD0C3-079F-4596-A5F0-1D12E18BEF99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3744EB7F-602A-40ED-ACA8-19FD7A0F2B0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{996D9A11-9D45-492A-B58B-49AD2EF068D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96B2455A-837F-4F30-94A4-21B29D7E9AAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F141B68A-1123-4D98-B8B4-F859044E0E84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB21F66C-B40A-410A-B3DE-577C8C5A1055}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="122" name="Picture 121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73331A61-AEE9-47CF-8F59-6D25B1DC6C96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D50F9B-8328-495C-90AE-51F58A6ADE8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 123">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A1632E6-4BBD-4B42-8C21-EFBEF56FCE62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 124">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAD220F-86F2-41A4-99E0-EC25BE5F6171}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="126" name="Picture 125">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BCB10A1-4305-4CAD-8A73-B95D4FD3092A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="127" name="Picture 126">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5FCD9A-18DF-4FF0-A979-CFEC0380FF67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="128" name="Picture 127">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94A48799-6595-4BF7-B225-D32930BDE21A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="129" name="Picture 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08074F8A-F55C-457F-85FE-701A0D0F582E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="130" name="Picture 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{244DFA43-92C1-4CD9-ABE0-A11D0E3508D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>91</xdr:col>
+      <xdr:colOff>1211581</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1169568" cy="1226820"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="131" name="Picture 130">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08FB31E6-2DE1-4EE6-9D12-D61862D1023F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="59047381" y="297180"/>
+          <a:ext cx="1169568" cy="1226820"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2120,13 +3256,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CM26"/>
+  <dimension ref="A1:CN26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="91" max="91" width="43.33203125" customWidth="1"/>
+    <col min="92" max="92" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2400,8 +3537,11 @@
       <c r="CM1" s="3" t="s">
         <v>194</v>
       </c>
+      <c r="CN1" s="4" t="s">
+        <v>195</v>
+      </c>
     </row>
-    <row r="2" spans="1:91" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:92" ht="112.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>562808</v>
       </c>
@@ -2673,7 +3813,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>369388</v>
       </c>
@@ -2945,7 +4085,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>776817</v>
       </c>
@@ -3217,7 +4357,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>733745</v>
       </c>
@@ -3489,7 +4629,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="6" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>625171</v>
       </c>
@@ -3761,7 +4901,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="7" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>892979</v>
       </c>
@@ -4033,7 +5173,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="8" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>550889</v>
       </c>
@@ -4305,7 +5445,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>236210</v>
       </c>
@@ -4577,7 +5717,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="10" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>964913</v>
       </c>
@@ -4849,7 +5989,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="11" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>175378</v>
       </c>
@@ -5121,7 +6261,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="12" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>785367</v>
       </c>
@@ -5393,7 +6533,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="13" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>828684</v>
       </c>
@@ -5665,7 +6805,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="14" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>618596</v>
       </c>
@@ -5937,7 +7077,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="15" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>444143</v>
       </c>
@@ -6209,7 +7349,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="16" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>846129</v>
       </c>
